--- a/excel_templates/用户表.xlsx
+++ b/excel_templates/用户表.xlsx
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>498</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>418</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>393</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3003,10 +3003,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>479</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>499</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3867,10 +3867,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -4539,10 +4539,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4923,10 +4923,10 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -5547,10 +5547,10 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>337</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -6027,10 +6027,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -6123,10 +6123,10 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -8139,10 +8139,10 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -8379,10 +8379,10 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -8475,10 +8475,10 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -8523,10 +8523,10 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>497</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -9099,10 +9099,10 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -9243,10 +9243,10 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -9435,10 +9435,10 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -9531,10 +9531,10 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -9675,10 +9675,10 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -9723,10 +9723,10 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>494</v>
+        <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -9915,10 +9915,10 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -9963,10 +9963,10 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -10059,10 +10059,10 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>331</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -10443,10 +10443,10 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>1065</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -10539,10 +10539,10 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>1837</v>
+        <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>956</v>
+        <v>0</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>1308</v>
+        <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -10635,10 +10635,10 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1113</v>
+        <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>971</v>
+        <v>0</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1717</v>
+        <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>1398</v>
+        <v>0</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -10731,10 +10731,10 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>727</v>
+        <v>0</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>954</v>
+        <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>702</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>471</v>
+        <v>0</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -10923,10 +10923,10 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>765</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>854</v>
+        <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -11019,10 +11019,10 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>518</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>489</v>
+        <v>0</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>911</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>542</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>492</v>
+        <v>0</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>901</v>
+        <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>852</v>
+        <v>0</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>749</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>723</v>
+        <v>0</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -11259,10 +11259,10 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>962</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -11307,10 +11307,10 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -11355,10 +11355,10 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -11403,10 +11403,10 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>926</v>
+        <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -11451,10 +11451,10 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>80199</v>
+        <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>74375</v>
+        <v>0</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -11499,10 +11499,10 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>50448</v>
+        <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>39106</v>
+        <v>0</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>96787</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>83754</v>
+        <v>0</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>30537</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>26500</v>
+        <v>0</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>31878</v>
+        <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>24350</v>
+        <v>0</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -11691,10 +11691,10 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>46710</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>35209</v>
+        <v>0</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>46304</v>
+        <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>37253</v>
+        <v>0</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -11787,10 +11787,10 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>47178</v>
+        <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -11835,10 +11835,10 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>21244</v>
+        <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>19398</v>
+        <v>0</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -11883,10 +11883,10 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>22292</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>19035</v>
+        <v>0</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -11931,10 +11931,10 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>29914</v>
+        <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>21096</v>
+        <v>0</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -11979,10 +11979,10 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>29574</v>
+        <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>24670</v>
+        <v>0</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -12027,10 +12027,10 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>26779</v>
+        <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>21950</v>
+        <v>0</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>26640</v>
+        <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>19909</v>
+        <v>0</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -12123,10 +12123,10 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>24178</v>
+        <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>20445</v>
+        <v>0</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -12171,10 +12171,10 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>28364</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>25299</v>
+        <v>0</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -12219,10 +12219,10 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>15733</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>13570</v>
+        <v>0</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -12267,10 +12267,10 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>14360</v>
+        <v>0</v>
       </c>
       <c r="G247" t="n">
-        <v>10638</v>
+        <v>0</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>10892</v>
+        <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>7627</v>
+        <v>0</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>15635</v>
+        <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>11877</v>
+        <v>0</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>15389</v>
+        <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>12469</v>
+        <v>0</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -12459,10 +12459,10 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>11007</v>
+        <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>8728</v>
+        <v>0</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -12507,10 +12507,10 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>19385</v>
+        <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>17502</v>
+        <v>0</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>12230</v>
+        <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>9813</v>
+        <v>0</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>18080</v>
+        <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>13508</v>
+        <v>0</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -12651,10 +12651,10 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>14269</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>13115</v>
+        <v>0</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>6582</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>5166</v>
+        <v>0</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -12747,10 +12747,10 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>9829</v>
+        <v>0</v>
       </c>
       <c r="G257" t="n">
-        <v>8112</v>
+        <v>0</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -12795,10 +12795,10 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>6184</v>
+        <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>4663</v>
+        <v>0</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -12843,10 +12843,10 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>7537</v>
+        <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>5955</v>
+        <v>0</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -12891,10 +12891,10 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>5564</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>4796</v>
+        <v>0</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -12939,10 +12939,10 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>5071</v>
+        <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>4553</v>
+        <v>0</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -12987,10 +12987,10 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>7601</v>
+        <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>7122</v>
+        <v>0</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -13035,10 +13035,10 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>9505</v>
+        <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>8722</v>
+        <v>0</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>8894</v>
+        <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>6756</v>
+        <v>0</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -13131,10 +13131,10 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>6607</v>
+        <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>5689</v>
+        <v>0</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -13179,10 +13179,10 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>6695</v>
+        <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>5249</v>
+        <v>0</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>5018</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>3865</v>
+        <v>0</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -13275,10 +13275,10 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>9655</v>
+        <v>0</v>
       </c>
       <c r="G268" t="n">
-        <v>8517</v>
+        <v>0</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -13323,10 +13323,10 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>7051</v>
+        <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>6509</v>
+        <v>0</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -13371,10 +13371,10 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>7681</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>6171</v>
+        <v>0</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>4826</v>
+        <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>3916</v>
+        <v>0</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -13467,10 +13467,10 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>4073</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>3591</v>
+        <v>0</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -13515,10 +13515,10 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>4607</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>3242</v>
+        <v>0</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -13563,10 +13563,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3984</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>3510</v>
+        <v>0</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -13611,10 +13611,10 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>3308</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>2510</v>
+        <v>0</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -13659,10 +13659,10 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>4519</v>
+        <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>3430</v>
+        <v>0</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -13707,10 +13707,10 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>4429</v>
+        <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>4106</v>
+        <v>0</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -13755,10 +13755,10 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3766</v>
+        <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>3541</v>
+        <v>0</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -13803,10 +13803,10 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3152</v>
+        <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>2493</v>
+        <v>0</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -13851,10 +13851,10 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3634</v>
+        <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>3171</v>
+        <v>0</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -13899,10 +13899,10 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>4011</v>
+        <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>2965</v>
+        <v>0</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -13947,10 +13947,10 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>4301</v>
+        <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>3177</v>
+        <v>0</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>3016</v>
+        <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>2217</v>
+        <v>0</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -14043,10 +14043,10 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>4868</v>
+        <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>4202</v>
+        <v>0</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -14091,10 +14091,10 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>4777</v>
+        <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>4210</v>
+        <v>0</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -14139,10 +14139,10 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>3187</v>
+        <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>2718</v>
+        <v>0</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -14187,10 +14187,10 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>4775</v>
+        <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>3879</v>
+        <v>0</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -14235,10 +14235,10 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>4880</v>
+        <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>3601</v>
+        <v>0</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -14283,10 +14283,10 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>4588</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>3288</v>
+        <v>0</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -14331,10 +14331,10 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>3377</v>
+        <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>2759</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -14379,10 +14379,10 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>2332</v>
+        <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>1806</v>
+        <v>0</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>2843</v>
+        <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>2361</v>
+        <v>0</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>2688</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>2026</v>
+        <v>0</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -14523,10 +14523,10 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>2020</v>
+        <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>1471</v>
+        <v>0</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -14571,10 +14571,10 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>2395</v>
+        <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>1884</v>
+        <v>0</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -14619,10 +14619,10 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>2056</v>
+        <v>0</v>
       </c>
       <c r="G296" t="n">
-        <v>1514</v>
+        <v>0</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -14667,10 +14667,10 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>2830</v>
+        <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>2274</v>
+        <v>0</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -14715,10 +14715,10 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>2682</v>
+        <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>2175</v>
+        <v>0</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -14763,10 +14763,10 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>2456</v>
+        <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>1849</v>
+        <v>0</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -14811,10 +14811,10 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>2458</v>
+        <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>2297</v>
+        <v>0</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -14859,10 +14859,10 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>2119</v>
+        <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>1739</v>
+        <v>0</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>2816</v>
+        <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -14955,10 +14955,10 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>2845</v>
+        <v>0</v>
       </c>
       <c r="G303" t="n">
-        <v>2425</v>
+        <v>0</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -15003,10 +15003,10 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>2053</v>
+        <v>0</v>
       </c>
       <c r="G304" t="n">
-        <v>1799</v>
+        <v>0</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -15051,10 +15051,10 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>2962</v>
+        <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>2295</v>
+        <v>0</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -15099,10 +15099,10 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>2510</v>
+        <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>2216</v>
+        <v>0</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -15147,10 +15147,10 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>2223</v>
+        <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>1827</v>
+        <v>0</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -15195,10 +15195,10 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>2283</v>
+        <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>1631</v>
+        <v>0</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>2204</v>
+        <v>0</v>
       </c>
       <c r="G309" t="n">
-        <v>1622</v>
+        <v>0</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -15291,10 +15291,10 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>2676</v>
+        <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>2535</v>
+        <v>0</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -15339,10 +15339,10 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2280</v>
+        <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>1884</v>
+        <v>0</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -15387,10 +15387,10 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2656</v>
+        <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>2246</v>
+        <v>0</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -15435,10 +15435,10 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>2408</v>
+        <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>1746</v>
+        <v>0</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -15483,10 +15483,10 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>2287</v>
+        <v>0</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2896</v>
+        <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>2598</v>
+        <v>0</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>

--- a/excel_templates/用户表.xlsx
+++ b/excel_templates/用户表.xlsx
@@ -510,7 +510,7 @@
         <v>74</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>

--- a/excel_templates/用户表.xlsx
+++ b/excel_templates/用户表.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
         <v>33</v>
@@ -519,7 +519,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
         <v>23</v>
